--- a/artfynd/A 7762-2024 artfynd.xlsx
+++ b/artfynd/A 7762-2024 artfynd.xlsx
@@ -2737,10 +2737,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120922481</v>
+        <v>120922487</v>
       </c>
       <c r="B20" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582249</v>
+        <v>582033</v>
       </c>
       <c r="R20" t="n">
-        <v>7194088</v>
+        <v>7194312</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120922487</v>
+        <v>120922481</v>
       </c>
       <c r="B21" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582033</v>
+        <v>582249</v>
       </c>
       <c r="R21" t="n">
-        <v>7194312</v>
+        <v>7194088</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2971,10 +2971,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120922483</v>
+        <v>120922484</v>
       </c>
       <c r="B22" t="n">
-        <v>79680</v>
+        <v>79642</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2983,25 +2983,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
         <v>582070</v>
       </c>
       <c r="R22" t="n">
-        <v>7194255</v>
+        <v>7194257</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120922484</v>
+        <v>120922485</v>
       </c>
       <c r="B23" t="n">
-        <v>79639</v>
+        <v>79718</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3099,21 +3099,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582070</v>
+        <v>582071</v>
       </c>
       <c r="R23" t="n">
         <v>7194257</v>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120922485</v>
+        <v>120922483</v>
       </c>
       <c r="B24" t="n">
-        <v>79715</v>
+        <v>79683</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3207,25 +3207,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582071</v>
+        <v>582070</v>
       </c>
       <c r="R24" t="n">
-        <v>7194257</v>
+        <v>7194255</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>

--- a/artfynd/A 7762-2024 artfynd.xlsx
+++ b/artfynd/A 7762-2024 artfynd.xlsx
@@ -2737,7 +2737,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120922487</v>
+        <v>120922481</v>
       </c>
       <c r="B20" t="n">
         <v>57351</v>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582033</v>
+        <v>582249</v>
       </c>
       <c r="R20" t="n">
-        <v>7194312</v>
+        <v>7194088</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120922481</v>
+        <v>120922485</v>
       </c>
       <c r="B21" t="n">
-        <v>57351</v>
+        <v>79718</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2866,43 +2866,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582249</v>
+        <v>582071</v>
       </c>
       <c r="R21" t="n">
-        <v>7194088</v>
+        <v>7194257</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2934,7 +2929,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2944,7 +2939,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2971,10 +2966,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120922484</v>
+        <v>120922483</v>
       </c>
       <c r="B22" t="n">
-        <v>79642</v>
+        <v>79683</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2983,25 +2978,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3014,7 +3009,7 @@
         <v>582070</v>
       </c>
       <c r="R22" t="n">
-        <v>7194257</v>
+        <v>7194255</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3083,10 +3078,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120922485</v>
+        <v>120922484</v>
       </c>
       <c r="B23" t="n">
-        <v>79718</v>
+        <v>79642</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3099,21 +3094,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3123,7 +3118,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582071</v>
+        <v>582070</v>
       </c>
       <c r="R23" t="n">
         <v>7194257</v>
@@ -3195,10 +3190,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120922483</v>
+        <v>120922487</v>
       </c>
       <c r="B24" t="n">
-        <v>79683</v>
+        <v>57351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3211,34 +3206,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582070</v>
+        <v>582033</v>
       </c>
       <c r="R24" t="n">
-        <v>7194255</v>
+        <v>7194312</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 7762-2024 artfynd.xlsx
+++ b/artfynd/A 7762-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115417711</v>
+        <v>115417805</v>
       </c>
       <c r="B2" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582076</v>
+        <v>582227</v>
       </c>
       <c r="R2" t="n">
-        <v>7194264</v>
+        <v>7194091</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115413251</v>
+        <v>115417672</v>
       </c>
       <c r="B3" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582099</v>
+        <v>582059</v>
       </c>
       <c r="R3" t="n">
-        <v>7194257</v>
+        <v>7194265</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115413303</v>
+        <v>120922483</v>
       </c>
       <c r="B4" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,43 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581907</v>
+        <v>582070</v>
       </c>
       <c r="R4" t="n">
-        <v>7194463</v>
+        <v>7194255</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,55 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115413294</v>
+        <v>115417787</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582563</v>
+        <v>581779</v>
       </c>
       <c r="R5" t="n">
-        <v>7193924</v>
+        <v>7194538</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,19 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115417804</v>
+        <v>115417790</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1177,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582390</v>
+        <v>581840</v>
       </c>
       <c r="R6" t="n">
-        <v>7194011</v>
+        <v>7194503</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,19 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115417787</v>
+        <v>115417792</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1289,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581779</v>
+        <v>582061</v>
       </c>
       <c r="R7" t="n">
-        <v>7194538</v>
+        <v>7194269</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,19 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115417799</v>
+        <v>115417793</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1401,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582227</v>
+        <v>582076</v>
       </c>
       <c r="R8" t="n">
-        <v>7194092</v>
+        <v>7194264</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,19 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115417792</v>
+        <v>115417795</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1513,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582061</v>
+        <v>582103</v>
       </c>
       <c r="R9" t="n">
-        <v>7194269</v>
+        <v>7194259</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1548,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,16 +1534,11 @@
         <v>115417797</v>
       </c>
       <c r="B10" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1697,19 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115417793</v>
+        <v>115417799</v>
       </c>
       <c r="B11" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1737,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582076</v>
+        <v>582227</v>
       </c>
       <c r="R11" t="n">
-        <v>7194264</v>
+        <v>7194092</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1772,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,19 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115417790</v>
+        <v>115417802</v>
       </c>
       <c r="B12" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1849,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581840</v>
+        <v>582231</v>
       </c>
       <c r="R12" t="n">
-        <v>7194503</v>
+        <v>7194065</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1884,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,59 +1852,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115413305</v>
+        <v>115417803</v>
       </c>
       <c r="B13" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582237</v>
+        <v>582273</v>
       </c>
       <c r="R13" t="n">
-        <v>7194070</v>
+        <v>7194059</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2005,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,19 +1959,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115417803</v>
+        <v>115417804</v>
       </c>
       <c r="B14" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2082,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582273</v>
+        <v>582390</v>
       </c>
       <c r="R14" t="n">
-        <v>7194059</v>
+        <v>7194011</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2117,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2127,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,55 +2066,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115413292</v>
+        <v>120922486</v>
       </c>
       <c r="B15" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582235</v>
+        <v>582067</v>
       </c>
       <c r="R15" t="n">
-        <v>7194066</v>
+        <v>7194258</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2229,22 +2131,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,59 +2173,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115417699</v>
+        <v>120922512</v>
       </c>
       <c r="B16" t="n">
-        <v>56470</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582177</v>
+        <v>581763</v>
       </c>
       <c r="R16" t="n">
-        <v>7194188</v>
+        <v>7194521</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2350,22 +2238,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,59 +2280,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115417674</v>
+        <v>120922592</v>
       </c>
       <c r="B17" t="n">
-        <v>55873</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581892</v>
+        <v>582324</v>
       </c>
       <c r="R17" t="n">
-        <v>7194495</v>
+        <v>7193983</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2471,22 +2345,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,15 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115417795</v>
+        <v>115413251</v>
       </c>
       <c r="B18" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2529,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2553,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582103</v>
+        <v>582099</v>
       </c>
       <c r="R18" t="n">
-        <v>7194259</v>
+        <v>7194257</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2625,37 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115417805</v>
+        <v>115417684</v>
       </c>
       <c r="B19" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2665,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582227</v>
+        <v>582060</v>
       </c>
       <c r="R19" t="n">
-        <v>7194091</v>
+        <v>7194265</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2700,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,55 +2601,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120922481</v>
+        <v>120922485</v>
       </c>
       <c r="B20" t="n">
-        <v>57351</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582249</v>
+        <v>582071</v>
       </c>
       <c r="R20" t="n">
-        <v>7194088</v>
+        <v>7194257</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2817,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2827,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2854,50 +2708,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120922485</v>
+        <v>115413292</v>
       </c>
       <c r="B21" t="n">
-        <v>79718</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582071</v>
+        <v>582235</v>
       </c>
       <c r="R21" t="n">
-        <v>7194257</v>
+        <v>7194066</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2924,22 +2778,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,15 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120922483</v>
+        <v>115413293</v>
       </c>
       <c r="B22" t="n">
-        <v>79683</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,34 +2831,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582070</v>
+        <v>582314</v>
       </c>
       <c r="R22" t="n">
-        <v>7194255</v>
+        <v>7194073</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3036,22 +2890,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3078,50 +2932,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120922484</v>
+        <v>115413294</v>
       </c>
       <c r="B23" t="n">
-        <v>79642</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582070</v>
+        <v>582563</v>
       </c>
       <c r="R23" t="n">
-        <v>7194257</v>
+        <v>7193924</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3148,22 +3002,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3190,15 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120922487</v>
+        <v>120922481</v>
       </c>
       <c r="B24" t="n">
-        <v>57351</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582033</v>
+        <v>582249</v>
       </c>
       <c r="R24" t="n">
-        <v>7194312</v>
+        <v>7194088</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3270,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3280,7 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3304,6 +3153,800 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120922487</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>582033</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7194312</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>115417699</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>582177</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7194188</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>115413303</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>581907</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7194463</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>115413305</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>582237</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7194070</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120922482</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>582136</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7194281</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>115417674</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>581892</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7194495</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120922484</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>582070</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7194257</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
